--- a/data/seed/portfolio/L-2025-4260/vypiska_2026-07_08.xlsx
+++ b/data/seed/portfolio/L-2025-4260/vypiska_2026-07_08.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ko'chirma" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Выписка" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -53,9 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -422,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -434,6 +435,7 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -446,217 +448,275 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>HISOB RAQAMIDAN KO'CHIRMA</t>
+          <t>ВЫПИСКА ПО РАСЧЕТНОМУ СЧЕТУ № 20208000659809820001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hisob raqami: 20208000659809820001</t>
+          <t>Клиент: Saodat Mebel MChJ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ИНН: 253676599</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mijoz: Saodat Mebel MChJ, STIR 253676599</t>
+          <t>Период: с 01.07.2026 по 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Davr: 01.07.2026 - 31.08.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Davr boshidagi qoldiq:</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
+          <t>Входящий остаток на 01.07.2026:</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>75400000</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>№ док.</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Дебет</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Наименование контрагента</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>ИНН контрагента</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>Счет контрагента</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>МФО банка</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>Назначение платежа</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>Остаток</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Sana</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Hujjat №</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Aylanma</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Kontragent</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>To'lov maqsadi</t>
-        </is>
+      <c r="A8" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n">
+        <v>4186000</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bahor Un Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>268678094</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>20208000756579124001</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Yetkazilan tovar uchun to'lov h/f №5519</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>79586000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Debet</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Kredit</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Nomi</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>STIR</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Hisob raqami</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>MFO</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n"/>
+      <c r="A9" s="3" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101</v>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>2912000</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Farg'ona Tekstil AJ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>208843068</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>20208000533582931001</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, h/f №8137 01.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>82498000</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>02.07.2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="A10" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>11396000</v>
+        <v>11480000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №217/26, НДС 12%</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9680</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>93978000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>02.07.2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="A11" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B11" t="n">
+        <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>9571000</v>
+        <v>2349000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SHARTNOMA №11/26 BO'YICHA OLDINDAN TO'LOV</t>
-        </is>
+          <t>Предоплата за товар по договору №3/26 от 02.07.2026</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>96327000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>28790000</v>
-      </c>
+      <c r="A12" s="3" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>13081000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
+          <t>Shahrisabz Tekstil AJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>384257887</t>
+          <t>242282445</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>20208000479782511001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -666,38 +726,37 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7955 за поставленный товар</t>
-        </is>
+          <t>Transport xizmatlari uchun to'lov, shartn. №27/26</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>83246000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="A13" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>5853000</v>
+        <v>25761000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Namangan Qog'oz MChJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>289361870</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000864737588001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -707,443 +766,432 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №5/26, НДС 12%</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8894</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>109007000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>9133000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="A14" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106</v>
+      </c>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>12213000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Qarshi Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>338185344</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000472487602001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №56/26</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №197/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>121220000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>06.07.2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>20980000</v>
-      </c>
-      <c r="D15" s="2" t="n"/>
+      <c r="A15" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107</v>
+      </c>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n">
+        <v>10711000</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №621</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8543</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>131931000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>07.07.2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>9950000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="A16" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B16" t="n">
+        <v>108</v>
+      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>7958000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №184/26</t>
-        </is>
+          <t>Оплата за товар по счет-фактуре №665 от 06.07.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>139889000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>07.07.2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>13629000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="A17" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B17" t="n">
+        <v>109</v>
+      </c>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>5335000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №147/26 от 07.07.2026, НДС 12%</t>
-        </is>
+          <t>Tovar uchun to'lov, hisob-faktura №6061 06.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>145224000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>08.07.2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="A18" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B18" t="n">
+        <v>110</v>
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>5099000</v>
+        <v>2433000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>239381853</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000474724876001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4056 за поставленный товар</t>
-        </is>
+          <t>Shartnoma №58/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>147657000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>08.07.2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>2074000</v>
-      </c>
+      <c r="A19" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B19" t="n">
+        <v>111</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>20980000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>384257887</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №167/26 от 08.07.2026</t>
-        </is>
+          <t>Iyun oyi uchun ish haqi, reestr №7803</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>126677000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>08.07.2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="A20" s="3" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B20" t="n">
+        <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>11037000</v>
+        <v>93636000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ishonch Farm Savdo MChJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>278450198</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000835986776001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №166/26</t>
-        </is>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №88/26</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>33041000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="A21" s="3" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B21" t="n">
+        <v>113</v>
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>116773000</v>
+        <v>3512000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>239381853</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000474724876001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8148 от 09.07.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Shartnoma №17/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>36553000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="A22" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B22" t="n">
+        <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>4448000</v>
+        <v>6762000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Namangan Qog'oz MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>289361870</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000864737588001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8249 от 09.07.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Shartnoma №207/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>43315000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>3588000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="A23" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B23" t="n">
+        <v>115</v>
+      </c>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>5193000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Barakali Qurilish AJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>260158065</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000542877358001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №223/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>48508000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="A24" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B24" t="n">
+        <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>44279000</v>
+        <v>2319000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1153,120 +1201,117 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №63/26 от 10.07.2026</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8868</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>50827000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>5753000</v>
-      </c>
+      <c r="A25" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B25" t="n">
+        <v>117</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>14416000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6206 за поставленный товар</t>
-        </is>
+          <t>Оплата за сырье по дог. №53/26 от 08.07.2026, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>36411000</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>13.07.2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="A26" s="3" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B26" t="n">
+        <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>8826000</v>
+        <v>6710000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Farg'ona Tekstil AJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>239381853</t>
+          <t>208843068</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000474724876001</t>
+          <t>20208000533582931001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4023 за поставленный товар</t>
-        </is>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №2637</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>43121000</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>13.07.2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>7542000</v>
-      </c>
+      <c r="A27" s="3" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B27" t="n">
+        <v>119</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>3588000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Oqtosh Qurilish MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>265518937</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000163951773001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1276,361 +1321,357 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №298/26, НДС 12%</t>
-        </is>
+          <t>Ijara haqi iyul oyi uchun, shartnoma №54/23</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>39533000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>13.07.2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>8556000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="A28" s="3" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B28" t="n">
+        <v>120</v>
+      </c>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>6343000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ishonch Farm Savdo MChJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>278450198</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000835986776001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №97/26</t>
-        </is>
+          <t>Tovar uchun to'lov, hisob-faktura №8165 10.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>45876000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>13.07.2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>10463000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="A29" s="3" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B29" t="n">
+        <v>121</v>
+      </c>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>3666000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barakali Un Mahsulotlari AJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>307445037</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000244013809001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №172/26 от 13.07.2026, НДС 12%</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №230/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>49542000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>13.07.2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="A30" s="3" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B30" t="n">
+        <v>122</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>14463000</v>
+        <v>17939000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zarafshon Non AJ</t>
+          <t>Shahrisabz Agro MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>292710962</t>
+          <t>289610808</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000544506327001</t>
+          <t>20208000706898370001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №45/26 от 13.07.2026, НДС 12%</t>
-        </is>
+          <t>Xom ashyo uchun to'lov, shartnoma №34/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>31603000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>13.07.2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>37611000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="A31" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B31" t="n">
+        <v>123</v>
+      </c>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>22522000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, h/f №8290 13.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>54125000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B32" t="n">
+        <v>124</v>
+      </c>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>17495000</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Bahor Un Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>268678094</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20208000756579124001</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №6874 13.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>71620000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B33" t="n">
+        <v>125</v>
+      </c>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n">
+        <v>7008000</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Bahor Un Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>268678094</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20208000756579124001</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Shartnoma №1/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>78628000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B34" t="n">
+        <v>126</v>
+      </c>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>14205000</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Bahor Un Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>268678094</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20208000756579124001</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartn. №218/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>92833000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B35" t="n">
+        <v>127</v>
+      </c>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>153873000</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Farg'ona Tekstil AJ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>208843068</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20208000533582931001</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>01121</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №9670</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>15.07.2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>20305000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Ishonch Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>278450198</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20208000835986776001</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №259/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>15.07.2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>26500000</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-4260)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>16307000253676599417</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Kredit shartnomasi L-2025-4260 bo'yicha navbatdagi to'lov (07.2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>16.07.2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>2861000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Социальный налог за июнь 2026 г.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>16.07.2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>2861000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>НДФЛ за июнь 2026</t>
-        </is>
+          <t>Tovar uchun to'lov, h/f №7070 15.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>246706000</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+      <c r="A36" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B36" t="n">
+        <v>128</v>
       </c>
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="n">
-        <v>2960000</v>
+        <v>12048000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1640,202 +1681,192 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Shartnoma №17/26 bo'yicha oldindan to'lov</t>
-        </is>
+          <t>TOVAR UCHUN TO'LOV, H/F №6592 15.07.2026, QQS BILAN</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>258754000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>17.07.2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="A37" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B37" t="n">
+        <v>129</v>
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>2473000</v>
+        <v>11516000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>384257887</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6538</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №174/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>270270000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>20.07.2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>11325000</v>
-      </c>
+      <c r="A38" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B38" t="n">
+        <v>130</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>2861000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9469 20.07.2026, QQS bilan</t>
-        </is>
+          <t>Ijtimoiy soliq iyun 2026</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>267409000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>20.07.2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>11316000</v>
-      </c>
+      <c r="A39" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B39" t="n">
+        <v>131</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>2861000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Namangan Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>289361870</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000864737588001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №6481 20.07.2026, QQS bilan</t>
-        </is>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>264548000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>20.07.2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A40" s="3" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B40" t="n">
+        <v>132</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>4648000</v>
+        <v>26500000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Farg'ona Non XK</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>307200158</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-4260)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000305473995001</t>
+          <t>16307000253676599417</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №155/26</t>
-        </is>
+          <t>Kredit shartnomasi L-2025-4260 bo'yicha navbatdagi to'lov (07.2026)</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>238048000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>21.07.2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="A41" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B41" t="n">
+        <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>4927000</v>
+        <v>9847000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1845,612 +1876,597 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7671 от 21.07.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1336</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>247895000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>21.07.2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="A42" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B42" t="n">
+        <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>3649000</v>
+        <v>8041000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>239381853</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000474724876001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7073 за поставленный товар</t>
-        </is>
+          <t>Предоплата за товар по договору №181/26 от 16.07.2026</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>255936000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>21.07.2026</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>5422000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="A43" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B43" t="n">
+        <v>135</v>
+      </c>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>2560000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3116</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №290/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>258496000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>21.07.2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
+      <c r="A44" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B44" t="n">
+        <v>136</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>5860000</v>
+        <v>57300000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
-        </is>
+          <t>Предоплата за материалы по договору №292/26</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>201196000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>22.07.2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>134433000</v>
-      </c>
+      <c r="A45" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B45" t="n">
+        <v>137</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>64364000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>239381853</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000474724876001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №183/26, НДС 12%</t>
-        </is>
+          <t>Xom ashyo uchun to'lov, shartnoma №151/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>136832000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>22.07.2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>119748000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="A46" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B46" t="n">
+        <v>138</v>
+      </c>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>5765000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №77/26 от 22.07.2026, НДС 12%</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №268/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>142597000</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="A47" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B47" t="n">
+        <v>139</v>
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>8912000</v>
+        <v>4022000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ziyo Mato MChJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>387955662</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000512046346001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2820 от 23.07.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Tovar uchun to'lov, h/f №2759 17.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>146619000</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="A48" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B48" t="n">
+        <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>3856000</v>
+        <v>3793000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Namangan Qog'oz MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>289361870</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000864737588001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №9774 17.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>150412000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B49" t="n">
+        <v>141</v>
+      </c>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>8618000</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Zafar Metall XK</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>395566205</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20208000204634696001</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>01153</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №291/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>2242000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>20208000911156427001</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
-        </is>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1339</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>159030000</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>6147000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="A50" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B50" t="n">
+        <v>142</v>
+      </c>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>6094000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sarbon Qurilish Materiallari MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>204826931</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000141670301001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4709</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №188/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>165124000</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="A51" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B51" t="n">
+        <v>143</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>64925000</v>
+        <v>26951000</v>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №142/26</t>
-        </is>
+          <t>Xom ashyo uchun to'lov, shartnoma №84/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>138173000</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>24.07.2026</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+      <c r="A52" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B52" t="n">
+        <v>144</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>10699000</v>
+        <v>2833000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>239381853</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000474724876001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №42/26 ОТ 24.07.2026</t>
-        </is>
+          <t>Shartnoma №116/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>141006000</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>24.07.2026</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>1967000</v>
-      </c>
+      <c r="A53" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B53" t="n">
+        <v>145</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>5883000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Buxoro Non MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>281088430</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000805335829001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №285/26, НДС 12%</t>
-        </is>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>135123000</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>27.07.2026</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>5895000</v>
-      </c>
+      <c r="A54" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B54" t="n">
+        <v>146</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>13005000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Shahrisabz Agro MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>289610808</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000706898370001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №238/26 от 27.07.2026</t>
-        </is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №173/26</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>122118000</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>27.07.2026</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>3524000</v>
-      </c>
+      <c r="A55" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B55" t="n">
+        <v>147</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>34617000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>384257887</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9015 за поставленный товар</t>
-        </is>
+          <t>Tovarlar uchun to'lov h/f №3107</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>87501000</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>27.07.2026</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
+      <c r="A56" s="3" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B56" t="n">
+        <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>2891000</v>
+        <v>4405000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2460,284 +2476,277 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №151/26, QQS 12%</t>
-        </is>
+          <t>Shartnoma №160/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>91906000</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>27.07.2026</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
+      <c r="A57" s="3" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B57" t="n">
+        <v>149</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>68101000</v>
+        <v>2242000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000550048269001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за товары соглано счет-фактуре №3107</t>
-        </is>
+          <t>Elektr energiyasi uchun to'lov</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>89664000</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>28.07.2026</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
+      <c r="A58" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B58" t="n">
+        <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>6247000</v>
+        <v>21885000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5531</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>111549000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B59" t="n">
+        <v>151</v>
+      </c>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>12830000</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Bahor Un Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>268678094</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20208000756579124001</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>00962</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4664 28.07.2026, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>28.07.2026</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>8142000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Ishonch Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>278450198</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>20208000835986776001</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №522</t>
-        </is>
+          <t>Shartnoma №31/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>124379000</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>28.07.2026</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>22426000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="A60" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B60" t="n">
+        <v>152</v>
+      </c>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>4006000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №99/26</t>
-        </is>
+          <t>Оплата за товар по счет-фактуре №6814 от 27.07.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>128385000</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>29.07.2026</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
+      <c r="A61" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B61" t="n">
+        <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>5427000</v>
+        <v>3990000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №733 от 29.07.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Tovar uchun to'lov, hisob-faktura №8936 27.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>132375000</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>30.07.2026</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
+      <c r="A62" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B62" t="n">
+        <v>154</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>3653000</v>
+        <v>3315000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>384257887</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №258/26, НДС 12%</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1050</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>135690000</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>31.07.2026</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
+      <c r="A63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B63" t="n">
+        <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>7825000</v>
+        <v>9794000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2747,38 +2756,37 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9427 за поставленный товар</t>
-        </is>
+          <t>Shartnoma №89/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>145484000</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>31.07.2026</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
+      <c r="A64" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B64" t="n">
+        <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>5957000</v>
+        <v>3314000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2788,74 +2796,77 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5193 за поставленный товар</t>
-        </is>
+          <t>Tovar uchun to'lov, h/f №813 29.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>148798000</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>31.07.2026</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
+      <c r="A65" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B65" t="n">
+        <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>300000</v>
+        <v>24232000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Tong Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
-        </is>
+          <t>Оплата за товары согласно счет-фактуре №8909</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>124566000</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>03.08.2026</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
+      <c r="A66" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B66" t="n">
+        <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>5451000</v>
+        <v>8861000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2865,38 +2876,37 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №67/26 от 03.08.2026</t>
-        </is>
+          <t>Tovar uchun to'lov, hisob-faktura №4725 30.07.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>133427000</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>03.08.2026</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
+      <c r="A67" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B67" t="n">
+        <v>159</v>
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>4688000</v>
+        <v>2353000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2906,161 +2916,152 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №206/26, НДС 12%</t>
-        </is>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №8667</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>135780000</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>03.08.2026</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n">
-        <v>2913000</v>
-      </c>
+      <c r="A68" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B68" t="n">
+        <v>160</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>78520000</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Buxoro Non MChJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>281088430</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000805335829001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4015 от 03.08.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Xom ashyo uchun to'lov, shartnoma №41/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>57260000</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>03.08.2026</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>4282000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="A69" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B69" t="n">
+        <v>161</v>
+      </c>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>5435000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ziyo Qurilish AJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>249251877</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000493820500001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №67/26 от 03.08.2026, НДС 12%</t>
-        </is>
+          <t>Shartnoma №102/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>62695000</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>03.08.2026</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="A70" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B70" t="n">
+        <v>162</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>275411000</v>
+        <v>300000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ziyo Qurilish AJ</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>249251877</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000493820500001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №287/26</t>
-        </is>
+          <t>Hisob-kassa xizmati uchun haq</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>62395000</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>04.08.2026</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
+      <c r="A71" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B71" t="n">
+        <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>4058000</v>
+        <v>12828000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3070,238 +3071,237 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9443 от 04.08.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4675</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>75223000</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>04.08.2026</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>2616000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="A72" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B72" t="n">
+        <v>164</v>
+      </c>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>10840000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №160/26</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5270</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>86063000</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>05.08.2026</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+      <c r="A73" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B73" t="n">
+        <v>165</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>2416000</v>
+        <v>60774000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ishonch Farm Savdo MChJ</t>
+          <t>Olmaliq Polimer MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>278450198</t>
+          <t>320015873</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000835986776001</t>
+          <t>20208000547399531001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №296/26</t>
-        </is>
+          <t>Tovarlar uchun to'lov h/ №7085</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>25289000</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>05.08.2026</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>20122000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="A74" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B74" t="n">
+        <v>166</v>
+      </c>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>196424000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №7/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>221713000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B75" t="n">
+        <v>167</v>
+      </c>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>8279000</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Farg'ona Tekstil AJ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>208843068</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20208000533582931001</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
           <t>01121</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>06.08.2026</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>6167000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Ziyo Qurilish AJ</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>249251877</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>20208000493820500001</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartn. №226/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>229992000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B76" t="n">
+        <v>168</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>8204000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Tong Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>336187018</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20208000473758832001</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t>01089</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №212/26 от 06.08.2026, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>5958000</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Tong Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>380686780</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>20208000487565791001</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №221/26 от 07.08.2026</t>
-        </is>
+          <t>Оплата за товары согласно счет-фактуре №9709</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>221788000</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="A77" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B77" t="n">
+        <v>169</v>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>4293000</v>
+        <v>5427000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3311,366 +3311,352 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №271/26 от 07.08.2026</t>
-        </is>
+          <t>Shartnoma №82/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>227215000</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>07.08.2026</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>3441000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="A78" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B78" t="n">
+        <v>170</v>
+      </c>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>3257000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Barakali Qurilish AJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>260158065</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000542877358001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4827</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>230472000</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>10.08.2026</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>12454000</v>
-      </c>
+      <c r="A79" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B79" t="n">
+        <v>171</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>20122000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>380686780</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9409 от 10.08.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Iyul oyi uchun ish haqi, reestr №8539</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>210350000</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>10.08.2026</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+      <c r="A80" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B80" t="n">
+        <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>11006000</v>
+        <v>12740000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>384257887</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №214/26, QQS 12%</t>
-        </is>
+          <t>Shartnoma №190/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>223090000</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>10.08.2026</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>6121000</v>
-      </c>
+      <c r="A81" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B81" t="n">
+        <v>173</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>38612000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Buxoro Non MChJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>281088430</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000805335829001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №175/26 от 10.08.2026</t>
-        </is>
+          <t>Transport xizmatlari uchun to'lov, shartn. №278/26</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>184478000</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>10.08.2026</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>4941000</v>
-      </c>
+      <c r="A82" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B82" t="n">
+        <v>174</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>41382000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Shahrisabz Agro MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>289610808</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000706898370001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Shartnoma №41/26 bo'yicha oldindan to'lov</t>
-        </is>
+          <t>Transport xizmatlari uchun to'lov, shartn. №167/26</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>143096000</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>10.08.2026</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
+      <c r="A83" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B83" t="n">
+        <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>3586000</v>
+        <v>11436000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>384257887</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №45/26 ОТ 10.08.2026</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartn. №121/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>154532000</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>10.08.2026</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v>1888000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="A84" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B84" t="n">
+        <v>176</v>
+      </c>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>7186000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ziyo Qurilish AJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>249251877</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000493820500001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №79/26</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №6/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>161718000</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>10.08.2026</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>10571000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="A85" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B85" t="n">
+        <v>177</v>
+      </c>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>6477000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9385</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8618</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>168195000</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>12.08.2026</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+      <c r="A86" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B86" t="n">
+        <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>20359000</v>
+        <v>5980000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3680,894 +3666,872 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Shartnoma №175/26 bo'yicha oldindan to'lov</t>
-        </is>
+          <t>Tovar uchun to'lov, hisob-faktura №9802 10.08.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>174175000</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>13.08.2026</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
+      <c r="A87" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B87" t="n">
+        <v>179</v>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>49806000</v>
+        <v>5259000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Qarshi Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>338185344</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000472487602001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №4051 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>179434000</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B88" t="n">
+        <v>180</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>3441000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Oqtosh Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>265518937</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>20208000163951773001</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
           <t>00962</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9348</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>14.08.2026</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>8761000</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Ilhom Sut AJ</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>384257887</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>20208000118199411001</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №195/26, QQS 12%</t>
-        </is>
+          <t>Bino ijarasi uchun to'lov avgust</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>175993000</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>15.08.2026</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
+      <c r="A89" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B89" t="n">
+        <v>181</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>26500000</v>
+        <v>6123000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-4260)</t>
+          <t>Tong Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>16307000253676599417</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-4260 bo'yicha navbatdagi to'lov (08.2026)</t>
-        </is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №83/26</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>169870000</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>27775000</v>
-      </c>
+      <c r="A90" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B90" t="n">
+        <v>182</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>8828000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №82/26, НДС 12%</t>
-        </is>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №204/26, QQS BILAN</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>161042000</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>9732000</v>
-      </c>
+      <c r="A91" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B91" t="n">
+        <v>183</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>14413000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Namangan Qog'oz MChJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>289361870</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000864737588001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №64/26, НДС 12%</t>
-        </is>
+          <t>Оплата за товары согласно счет-фактуре №317</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>146629000</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
+      <c r="A92" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B92" t="n">
+        <v>184</v>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>8224000</v>
+        <v>16416000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Qarshi Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>338185344</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000472487602001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
-        </is>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №8953</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>163045000</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
+      <c r="A93" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B93" t="n">
+        <v>185</v>
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>5240000</v>
+        <v>11548000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №248/26, НДС 12%</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №128/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>174593000</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
+      <c r="A94" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B94" t="n">
+        <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>2585000</v>
+        <v>5576000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Buxoro Non MChJ</t>
+          <t>Qarshi Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>281088430</t>
+          <t>338185344</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000805335829001</t>
+          <t>20208000472487602001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Shartnoma №196/26 bo'yicha oldindan to'lov</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №20/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>180169000</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v>2453000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="A95" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B95" t="n">
+        <v>187</v>
+      </c>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>40482000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №28/26</t>
-        </is>
+          <t>Shartnoma №205/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>220651000</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v>2744000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="A96" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B96" t="n">
+        <v>188</v>
+      </c>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>12374000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
-        </is>
+          <t>Tovar uchun to'lov, hisob-faktura №4148 13.08.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>233025000</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
+      <c r="A97" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B97" t="n">
+        <v>189</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>2744000</v>
+        <v>26500000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-4260)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000253676599417</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
-        </is>
+          <t>Kredit shartnomasi L-2025-4260 bo'yicha navbatdagi to'lov (08.2026)</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>206525000</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v>4644000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="A98" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B98" t="n">
+        <v>190</v>
+      </c>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>8069000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ishonch Farm Savdo MChJ</t>
+          <t>Farg'ona Tekstil AJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>278450198</t>
+          <t>208843068</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000835986776001</t>
+          <t>20208000533582931001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №107/26 ОТ 17.08.2026, НДС 12%</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №132/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>214594000</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>17.08.2026</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>6838000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="A99" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B99" t="n">
+        <v>191</v>
+      </c>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>7854000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ishonch Farm Savdo MChJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>278450198</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000835986776001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №43/26</t>
-        </is>
+          <t>SHARTNOMA №156/26 BO'YICHA OLDINDAN TO'LOV</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>222448000</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>18.08.2026</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v>11289000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="A100" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B100" t="n">
+        <v>192</v>
+      </c>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>6254000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ziyo Qurilish AJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>249251877</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000493820500001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7609</t>
-        </is>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1768</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>228702000</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>19.08.2026</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
+      <c r="A101" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B101" t="n">
+        <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>21702000</v>
+        <v>5991000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>384257887</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3777 от 19.08.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №250/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>234693000</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>20.08.2026</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="A102" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B102" t="n">
+        <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>4914000</v>
+        <v>5658000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Namangan Qog'oz MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>289361870</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000864737588001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8960 за поставленный товар</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №122/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>240351000</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>20.08.2026</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>4231000</v>
-      </c>
+      <c r="A103" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B103" t="n">
+        <v>195</v>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>2744000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>384257887</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №7196 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
-        </is>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>237607000</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>20.08.2026</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>4117000</v>
-      </c>
+      <c r="A104" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B104" t="n">
+        <v>196</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>2744000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8554 от 20.08.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>JShDS iyul oyi uchun</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>234863000</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>20.08.2026</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
+      <c r="A105" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B105" t="n">
+        <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>4819000</v>
+        <v>4480000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №6794</t>
-        </is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №42/26</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>230383000</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>21.08.2026</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v>18734000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="A106" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B106" t="n">
+        <v>198</v>
+      </c>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>5650000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3136</t>
-        </is>
+          <t>Оплата по счет-фактуре №4570 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>236033000</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>24.08.2026</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>13854000</v>
-      </c>
+      <c r="A107" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B107" t="n">
+        <v>199</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>12058000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ziyo Mato MChJ</t>
+          <t>Shahrisabz Agro MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>387955662</t>
+          <t>289610808</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000512046346001</t>
+          <t>20208000706898370001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3550 от 24.08.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Xom ashyo uchun to'lov, shartn. №253/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>223975000</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>24.08.2026</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
+      <c r="A108" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B108" t="n">
+        <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>9665000</v>
+        <v>14506000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Bahor Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>268678094</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000756579124001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4577,243 +4541,237 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №53/26 от 24.08.2026</t>
-        </is>
+          <t>Shartnoma №240/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>238481000</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>24.08.2026</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n">
-        <v>6563000</v>
-      </c>
+      <c r="A109" s="3" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B109" t="n">
+        <v>201</v>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>5750000</v>
+      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Namangan Qog'oz MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>289361870</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000864737588001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №199/26, QQS 12%</t>
-        </is>
+          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>232731000</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>24.08.2026</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="A110" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B110" t="n">
+        <v>202</v>
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>4286000</v>
+        <v>3840000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №50/26 ОТ 24.08.2026</t>
-        </is>
+          <t>Tovar uchun to'lov, hisob-faktura №9506 24.08.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>236571000</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>24.08.2026</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>2471000</v>
-      </c>
+      <c r="A111" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B111" t="n">
+        <v>203</v>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>4450000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
+          <t>Shahrisabz Agro MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>384257887</t>
+          <t>289610808</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>20208000706898370001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №220/26, НДС 12%</t>
-        </is>
+          <t>Tovarlar uchun to'lov h/f №1388</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>232121000</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>24.08.2026</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
+      <c r="A112" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B112" t="n">
+        <v>204</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>4130000</v>
+        <v>19938000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1554</t>
-        </is>
+          <t>Materiallar uchun oldindan to'lov, shartn. №103/26</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>212183000</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>24.08.2026</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
+      <c r="A113" s="3" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B113" t="n">
+        <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>5694000</v>
+        <v>92695000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shahrisabz Agro MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>289610808</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000706898370001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
-        </is>
+          <t>Оплата за транспортные услуги по договору №200/26</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>119488000</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>24.08.2026</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
+      <c r="A114" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B114" t="n">
+        <v>206</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>46461000</v>
+        <v>8061000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ziyo Qurilish AJ</t>
+          <t>Tong Tur Servis AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>249251877</t>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000493820500001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -4823,161 +4781,157 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6775</t>
-        </is>
+          <t>Tovarlar uchun to'lov h/f №4215</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>111427000</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>25.08.2026</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>3052000</v>
-      </c>
+      <c r="A115" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B115" t="n">
+        <v>207</v>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>18201000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ilhom Sut AJ</t>
+          <t>Shahrisabz Agro MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>384257887</t>
+          <t>289610808</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000118199411001</t>
+          <t>20208000706898370001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3589 от 25.08.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №149/26</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>93226000</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>25.08.2026</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v>2151000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="A116" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B116" t="n">
+        <v>208</v>
+      </c>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>8650000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000911156427001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ ЗА АВГУСТ 2026 Г.</t>
-        </is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8653</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>101876000</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>26.08.2026</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
+      <c r="A117" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B117" t="n">
+        <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>9387000</v>
+        <v>4023000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Farg'ona Tekstil AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>208843068</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000533582931001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4851 26.08.2026, QQS bilan</t>
-        </is>
+          <t>Shartnoma №238/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>105899000</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>26.08.2026</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>4319000</v>
-      </c>
+      <c r="A118" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B118" t="n">
+        <v>210</v>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>2151000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>239381853</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000474724876001</t>
+          <t>20208000550048269001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4987,391 +4941,385 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №240/26 от 26.08.2026</t>
-        </is>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>103748000</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>26.08.2026</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
+      <c r="A119" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B119" t="n">
+        <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>2839000</v>
+        <v>18261000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tong Tekstil MChJ</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>380686780</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000487565791001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №6967 ОТ 27.08.2026, В Т.Ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>122009000</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B120" t="n">
+        <v>212</v>
+      </c>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>5349000</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Bahor Un Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>268678094</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>20208000756579124001</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
           <t>00962</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №263/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>26.08.2026</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v>2802000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Zarafshon Non AJ</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>292710962</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>20208000544506327001</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №39/26 от 26.08.2026, НДС 12%</t>
-        </is>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №171/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>127358000</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>27.08.2026</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>149032000</v>
-      </c>
+      <c r="A121" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B121" t="n">
+        <v>213</v>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>5675000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ziyo Mato MChJ</t>
+          <t>Bekobod Qurilish AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>387955662</t>
+          <t>271096275</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000512046346001</t>
+          <t>20208000450632716001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №235/26 от 27.08.2026</t>
-        </is>
+          <t>TOVARLAR UCHUN TO'LOV H/F №6527</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>121683000</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>27.08.2026</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n">
-        <v>3511000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="A122" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B122" t="n">
+        <v>214</v>
+      </c>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>9107000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish Materiallari AJ</t>
+          <t>Zafar Metall XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>311896108</t>
+          <t>395566205</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000837068983001</t>
+          <t>20208000204634696001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7741</t>
-        </is>
+          <t>Mahsulot uchun to'lov, shartnoma №147/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>130790000</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>28.08.2026</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
+      <c r="A123" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B123" t="n">
+        <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>11095000</v>
+        <v>3408000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kamalak Qurilish Materiallari XK</t>
+          <t>Xiva Yog'och AJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>239381853</t>
+          <t>225788761</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000474724876001</t>
+          <t>20208000819941115001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №450 31.08.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>134198000</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B124" t="n">
+        <v>216</v>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Navbahor Bank ATB</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Hisob-kassa xizmati uchun haq</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>133898000</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B125" t="n">
+        <v>217</v>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>12419000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Tong Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>336187018</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>20208000473758832001</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №135/26</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>121479000</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B126" t="n">
+        <v>218</v>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>22774000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Angren Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>344503772</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>20208000401380994001</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
           <t>00987</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №89/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>31.08.2026</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>14190000</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Tong Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>380686780</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>20208000487565791001</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №279/26 от 31.08.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>31.08.2026</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>6281000</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Tong Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>380686780</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>20208000487565791001</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №97/26, НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>31.08.2026</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>4537000</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Tong Tekstil MChJ</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>380686780</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>20208000487565791001</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6870 от 31.08.2026, в т.ч. НДС 12%</t>
-        </is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №140/26</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>98705000</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>31.08.2026</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
+      <c r="A127" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B127" t="n">
+        <v>219</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>300000</v>
+        <v>33105000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Tong Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>336187018</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000473758832001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>КОМИССИЯ ЗА ПЕРЕВОД</t>
-        </is>
+          <t>Xom ashyo uchun to'lov, shartn. №77/26, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>65600000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
+          <t>Итого обороты:</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>972626000</v>
+        <v>979220000</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>962826000</v>
+        <v>969420000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Davr oxiridagi qoldiq:</t>
+          <t>Исходящий остаток на 31.08.2026:</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
@@ -5380,10 +5328,6 @@
       <c r="D129" s="4" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:H8"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>